--- a/www/download/COUNTRY.GBR.rpO1.xlsx
+++ b/www/download/COUNTRY.GBR.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>Reino Unido</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.213</t>
+          <t>0.633524869461459</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>0.640311429707812</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>0.610612454449238</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.603715279744235</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>0.617962958901194</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.65958277227438</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>0.694463734373446</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>0.66610712183995</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.611856564104196</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.545911129989382</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.549329817675818</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.542702541368262</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.499580378014237</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.539595512385694</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.639190041391055</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>27.913</t>
+          <t>2.19074612757621</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>28.164</t>
+          <t>2.06532992583113</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>2.04387854763905</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>2.03178920076106</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>29.267</t>
+          <t>2.17525839173459</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>29.617</t>
+          <t>2.12276054683173</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>29.925</t>
+          <t>2.07566828117046</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>30.106</t>
+          <t>2.15208444270866</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>30.408</t>
+          <t>2.24362638615959</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>30.703</t>
+          <t>2.15234690541774</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>31.09</t>
+          <t>2.17482290742738</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>31.398</t>
+          <t>2.13305102197436</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>31.602</t>
+          <t>2.10110571434112</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>31.674</t>
+          <t>1.97695046159939</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>30.972</t>
+          <t>1.96506964250071</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>23.964</t>
+          <t>3.80705492960141</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>24.245</t>
+          <t>3.73882535205606</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>3.62616154552461</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>25.156</t>
+          <t>3.63702219790741</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25.577</t>
+          <t>3.81871398335734</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>26.013</t>
+          <t>3.79506657109954</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>26.297</t>
+          <t>3.66984920540456</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>26.409</t>
+          <t>3.77016669364873</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26.475</t>
+          <t>3.91225825568978</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26.731</t>
+          <t>3.76877515627261</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>27.093</t>
+          <t>3.82744890584089</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>27.31</t>
+          <t>3.74238375309216</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>27.438</t>
+          <t>3.63741763954978</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>27.505</t>
+          <t>3.61744055259243</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>26.766</t>
+          <t>3.49317239255813</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>44993.802</t>
+          <t>4.57035638785739</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45389.552</t>
+          <t>4.42580421164948</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>46176.543</t>
+          <t>4.37093788018888</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>46487.59</t>
+          <t>4.47104273440305</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>46808.741</t>
+          <t>4.63151235884164</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>47050.896</t>
+          <t>4.54623143238691</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>47522.65</t>
+          <t>4.36209560749529</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>47355.712</t>
+          <t>4.41371008419632</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>47271.276</t>
+          <t>4.59084327875404</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>47631.936</t>
+          <t>4.43867213638736</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>48233.604</t>
+          <t>4.47643907813903</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>48510.801</t>
+          <t>4.39289625973844</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>48898.444</t>
+          <t>4.27814230015979</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>48638.184</t>
+          <t>4.16847857277338</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>47697.788</t>
+          <t>4.06022792386811</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>38627.754</t>
+          <t>48455923303399.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>39074.066</t>
+          <t>44516533631290.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39982.918</t>
+          <t>49932966380959.9</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>40493.614</t>
+          <t>58809616511585.3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>40906.739</t>
+          <t>64388451996073</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>41325.285</t>
+          <t>72220728836614.2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>41761.52</t>
+          <t>75815201484467.8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>41540.623</t>
+          <t>78587090908691.7</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>41156.943</t>
+          <t>84998014144863.6</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>41469.329</t>
+          <t>83849499260141.4</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>42032.235</t>
+          <t>80644299120837.8</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>42194.369</t>
+          <t>73519453578153.4</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>42455.417</t>
+          <t>62835582739004</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>42236.584</t>
+          <t>42864712442778.8</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>41220.09</t>
+          <t>35449052129856.8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>10933093092395.5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>10153864784165.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>11636517389005.2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>14163884418225.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>15670878923578</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>34.75</t>
+          <t>17842601385473.7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>19191142119423.3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>20047810008002.6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>36.19</t>
+          <t>21755120353613.3</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>21189283187640.8</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>36.18</t>
+          <t>19764632657062.3</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>37.24</t>
+          <t>18014258295139.3</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>38.95</t>
+          <t>15448917741890.8</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>10936625842836.3</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>39.84</t>
+          <t>9026515844833.96</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>41.53</t>
+          <t>927978540.449774</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>41.62</t>
+          <t>814457234.299711</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>43.54</t>
+          <t>845996464.58717</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>43.37</t>
+          <t>976537874.664369</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>1064162347.34642</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>42.01</t>
+          <t>1208881042.86511</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>41.22</t>
+          <t>1296362387.00332</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>1245406450.65341</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>1178891179.76918</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>978453402.459873</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>44.49</t>
+          <t>889764778.013889</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>44.26</t>
+          <t>762660657.027313</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>572037548.001835</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>410155851.612738</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>428084506.950752</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>1331662.62476976</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>1381969.30685058</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>1546717.51716233</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>1687121.11374715</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>23.88</t>
+          <t>1736497.22132131</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>1736506.9175088</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>23.77</t>
+          <t>1743237.15761697</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>1912487.03640194</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>2196997.29974511</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>2603823.26417647</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>19.33</t>
+          <t>2739094.35520131</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>2924174.07653427</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>18.81</t>
+          <t>3348212.53002904</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>18.34</t>
+          <t>3177127.59304861</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>2760776.62815445</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>2178417.55997443</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>2247895.08473401</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.38</t>
+          <t>2468434.00415673</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>2638357.77877417</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>2692628.63670575</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>24.34</t>
+          <t>2662974.81989724</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>24.87</t>
+          <t>2643403.21506474</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>2864794.34895275</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>3255648.42998579</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>3860141.92122834</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>4155799.54074163</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>4394729.45293634</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>5009050.63975796</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>4552568.62771302</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>3919755.86344081</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>43.32</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46.33</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>46.37</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>44.98</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>45.54</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>47.67</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>49.23</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>46.84</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>47.21</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>47.98</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>212500.162011772</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>36.86</t>
+          <t>224602.795790781</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>237166.043027899</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>253307.032621812</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>30.58</t>
+          <t>252781.185252721</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>29.85</t>
+          <t>239970.98559699</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>221271.799996857</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28.65</t>
+          <t>228901.138099981</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>26.38</t>
+          <t>249466.205245908</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>297167.948036634</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>300280.684492764</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>303938.098384946</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>358119.468280028</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.633524869461459</t>
+          <t>456229.890352006</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.640311429707812</t>
+          <t>418802.424589205</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.610612454449238</t>
+          <t>469403.686527035</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.603715279744235</t>
+          <t>563041.994682192</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.617962958901194</t>
+          <t>612694.175375453</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.65958277227438</t>
+          <t>685910.943969312</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.694463734373446</t>
+          <t>729784.466647271</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.66610712183995</t>
+          <t>759127.949108356</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.611856564104196</t>
+          <t>821723.148389549</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.545911129989382</t>
+          <t>792685.765128158</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.549329817675818</t>
+          <t>729510.6727591</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.542702541368262</t>
+          <t>659621.321682143</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.499580378014237</t>
+          <t>563048.244838938</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.539595512385694</t>
+          <t>397623.190068581</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.639190041391055</t>
+          <t>337238.132139055</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>218867887473.894</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>568665787375.706</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>669995918266.715</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>273708999486.839</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.802</t>
+          <t>436600069954.527</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.807</t>
+          <t>580118501453.223</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>800907569460.513</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>913090038040.483</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.008</t>
+          <t>1032376509747.74</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.188</t>
+          <t>966660750786.327</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.246</t>
+          <t>335749231444.778</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>598276176501.774</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>609693330792.49</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>686968586023.554</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.223</t>
+          <t>202351705379.239</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>-200596421707.828</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.729</t>
+          <t>76200962629.1974</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>-86118976909.7998</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-669688053249.276</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>-832915528551.159</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>-925253802339.571</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>-898762457862.969</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.003</t>
+          <t>-1048248531411.75</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.156</t>
+          <t>-1203285795695.6</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>-1234906258981.09</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.426</t>
+          <t>-1503843983103</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.523</t>
+          <t>-1396285296358.75</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.751</t>
+          <t>-1390769797163.59</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.658</t>
+          <t>-889852873884.478</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.416</t>
+          <t>-1018383352818.91</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.764</t>
+          <t>419464309181.722</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.874</t>
+          <t>492464824746.508</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3.104</t>
+          <t>756114895176.515</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3.286</t>
+          <t>943397052736.115</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>3.374</t>
+          <t>1269515598505.69</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3.316</t>
+          <t>1505372303792.79</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1699670027323.48</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3.579</t>
+          <t>1961338569452.23</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.115</t>
+          <t>2235662305443.34</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4.905</t>
+          <t>2201567009767.41</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5.125</t>
+          <t>1839593214547.78</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>5.395</t>
+          <t>1994561472860.52</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>6.298</t>
+          <t>2000463127956.08</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1576821459908.03</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1220735058198.15</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2.101</t>
+          <t>2045040.28175542</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.221</t>
+          <t>1821573.97004062</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1988994.10187036</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2.637</t>
+          <t>2372922.59378208</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>2663461.12614252</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.688</t>
+          <t>2923322.35367793</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.669</t>
+          <t>3026590.76716958</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.909</t>
+          <t>3192992.32073069</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>3.332</t>
+          <t>3553171.90146289</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3.942</t>
+          <t>3328266.14452475</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>4.192</t>
+          <t>3083767.85462698</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4.487</t>
+          <t>2732521.33075703</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>2280626.46772189</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>4.909</t>
+          <t>1570514.17755304</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.002</t>
+          <t>1303975.57874689</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1.048</t>
+          <t>2057421.34337617</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1911304.71146169</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.217</t>
+          <t>2190867.162143</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>2668032.77462174</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>2968876.89878045</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>3402283.85510269</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>3644895.62256359</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.458</t>
+          <t>3802654.48342417</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>4147658.70027281</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.005</t>
+          <t>4073468.98596623</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.073</t>
+          <t>3773543.95721154</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>3441360.08232167</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2.557</t>
+          <t>2959998.32116596</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2.452</t>
+          <t>2097256.6647204</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.008</t>
+          <t>1793879.04422424</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>219.07</t>
+          <t>302968.846362564</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>206.53</t>
+          <t>334168.171598558</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>204.39</t>
+          <t>362418.111046132</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>203.18</t>
+          <t>360604.193608908</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>217.53</t>
+          <t>365500.987238348</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>212.28</t>
+          <t>378672.434444504</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>207.57</t>
+          <t>368615.603568295</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>215.21</t>
+          <t>386747.802219923</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>224.36</t>
+          <t>443194.281960158</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>215.23</t>
+          <t>523620.734790844</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>217.48</t>
+          <t>547244.802844159</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>213.31</t>
+          <t>607572.724619445</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>210.11</t>
+          <t>703544.645994065</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>197.7</t>
+          <t>737461.648794785</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>196.51</t>
+          <t>572279.820996099</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>380.71</t>
+          <t>9656026950065.39</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>373.88</t>
+          <t>9144353193427.51</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>362.62</t>
+          <t>10160315326987.6</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>363.7</t>
+          <t>11468597087264.8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>381.87</t>
+          <t>12259206239577.2</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>379.51</t>
+          <t>14218651841109.9</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>366.98</t>
+          <t>14578752122724.5</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>377.02</t>
+          <t>14570162851734.4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>391.23</t>
+          <t>15782413907039.8</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>376.88</t>
+          <t>14482524414804.9</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>382.74</t>
+          <t>13843324071448.9</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>374.24</t>
+          <t>12773198964697.4</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>363.74</t>
+          <t>10654997410021.6</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>361.74</t>
+          <t>8018581284573.19</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>349.32</t>
+          <t>6454873873189.85</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>457.04</t>
+          <t>286045.401442143</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>442.58</t>
+          <t>313056.00743486</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>437.09</t>
+          <t>330836.790070265</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>447.1</t>
+          <t>345103.027382917</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>463.15</t>
+          <t>356517.811334066</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>454.62</t>
+          <t>372960.94236261</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>436.21</t>
+          <t>369101.953496387</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>441.37</t>
+          <t>391838.926787815</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>459.08</t>
+          <t>441883.051931132</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>443.87</t>
+          <t>534548.962064389</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>447.64</t>
+          <t>574998.747413278</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>439.29</t>
+          <t>632001.053436416</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>427.81</t>
+          <t>729681.255202372</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>416.85</t>
+          <t>748582.506174736</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>406.02</t>
+          <t>577281.317174778</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>57429599.716</t>
+          <t>9257240815773.62</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>53829383.813</t>
+          <t>9025927936743.82</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>62724831.005</t>
+          <t>9777527740497.05</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>77051879.776</t>
+          <t>11160992119138.8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>86890819.215</t>
+          <t>12333090853142.7</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>100765769.381</t>
+          <t>14538877797998.6</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>109072598.271</t>
+          <t>15403458019062.5</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>114482257.81</t>
+          <t>15723427874829.1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>126122683.432</t>
+          <t>16756523850469.3</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>125069336.713</t>
+          <t>15847513664124.3</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>117320454.809</t>
+          <t>15078406873887.7</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>108052735.454</t>
+          <t>14046332421507.1</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>93541825.678</t>
+          <t>11796324949949.6</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>66428094.3</t>
+          <t>8872747280440.65</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>55560473.06</t>
+          <t>6731216804358.6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>49007345.312</t>
+          <t>16923.4449204217</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>44164060.904</t>
+          <t>21112.1641636981</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>49307163.785</t>
+          <t>31581.3209758671</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>59693240.769</t>
+          <t>15501.166225991</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>68123345.223</t>
+          <t>8983.17590428165</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>76044384.386</t>
+          <t>5711.49208189395</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>79590257.404</t>
+          <t>-486.349928091777</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>84323734.198</t>
+          <t>-5091.12456789178</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>94070226.091</t>
+          <t>1311.23002902552</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>88967882.309</t>
+          <t>-10928.2272735449</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>83548522.485</t>
+          <t>-27753.9445691197</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>74625157.543</t>
+          <t>-24428.3288169715</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>62575829.021</t>
+          <t>-26136.6092083064</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>43196992.454</t>
+          <t>-11120.8573799519</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>34902210.341</t>
+          <t>-5001.49617867885</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>48455923.303</t>
+          <t>398786134291.778</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>44516533.631</t>
+          <t>118425256683.694</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>49932966.381</t>
+          <t>382787586490.557</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>58809616.512</t>
+          <t>307604968125.994</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>64388451.996</t>
+          <t>-73884613565.5484</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>72220728.837</t>
+          <t>-320225956888.718</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>75815201.484</t>
+          <t>-824705896337.994</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78587090.909</t>
+          <t>-1153265023094.76</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>84998014.145</t>
+          <t>-974109943429.493</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>83849499.26</t>
+          <t>-1364989249319.4</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>80644299.121</t>
+          <t>-1235082802438.87</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>73519453.578</t>
+          <t>-1273133456809.77</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>62835582.739</t>
+          <t>-1141327539927.98</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>42864712.443</t>
+          <t>-854165995867.458</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>35449052.13</t>
+          <t>-276342931168.75</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2.178</t>
+          <t>497131.41044</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.248</t>
+          <t>516670.71791</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2.468</t>
+          <t>559244.04591</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2.638</t>
+          <t>578765.90324</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.693</t>
+          <t>580780.17479</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.663</t>
+          <t>570505.03286</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.643</t>
+          <t>556625.6481</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2.865</t>
+          <t>594832.15011</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3.256</t>
+          <t>671468.75727</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>786803.00218</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>4.156</t>
+          <t>820056.55398</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>4.395</t>
+          <t>876941.47773</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>5.009</t>
+          <t>989863.96314</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>4.553</t>
+          <t>939376.0817</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>748813.66309</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>29621016.281</t>
+          <t>0.0470951134000004</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>27368040.236</t>
+          <t>0.0509666180847551</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>31287931.399</t>
+          <t>0.0554210457307447</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>37606327.128</t>
+          <t>0.0539449418750565</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>41524615.185</t>
+          <t>0.0526766993459328</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>47094623.004</t>
+          <t>0.0516571223830756</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>49997622.605</t>
+          <t>0.0545793368206159</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>52463379.316</t>
+          <t>0.0633824406813315</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>57358898.412</t>
+          <t>0.0679132053844368</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>56559909.278</t>
+          <t>0.070261039215943</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>53152791.018</t>
+          <t>0.0675504766851976</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>48918524.468</t>
+          <t>0.0737477222730851</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>42001349.275</t>
+          <t>0.0710262202283211</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>29914246.617</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>24967604.621</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.332</t>
+          <t>609344.664262209</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.382</t>
+          <t>630766.500194064</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.547</t>
+          <t>704156.9451464</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.687</t>
+          <t>772019.549801978</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.736</t>
+          <t>802302.130258525</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.737</t>
+          <t>806841.874751881</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.743</t>
+          <t>812416.796848852</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.912</t>
+          <t>881834.139782243</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2.197</t>
+          <t>1008231.40487965</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2.604</t>
+          <t>1188319.79474407</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2.739</t>
+          <t>1246278.60661961</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2.924</t>
+          <t>1327141.80120477</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>3.348</t>
+          <t>1520317.19677425</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>3.177</t>
+          <t>1439534.76037267</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.761</t>
+          <t>1222888.6709742</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10933093.092</t>
+          <t>704861.697415182</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10153864.784</t>
+          <t>729241.42651865</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11636517.389</t>
+          <t>808232.241464891</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>14163884.418</t>
+          <t>880232.972086167</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>15670878.924</t>
+          <t>912758.829648804</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>17842601.385</t>
+          <t>914475.288209213</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>19191142.119</t>
+          <t>920938.425083602</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>20047810.008</t>
+          <t>1002647.46318871</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>21755120.354</t>
+          <t>1155969.91713234</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>21189283.188</t>
+          <t>1362823.71365045</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>19764632.657</t>
+          <t>1426225.38972571</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>18014258.295</t>
+          <t>1522740.61097274</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>15448917.742</t>
+          <t>1751292.93512564</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>10936625.843</t>
+          <t>1657762.14653244</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>9026515.845</t>
+          <t>1415851.85917085</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>2763663.07938533</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>2874492.27388289</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>3103675.08207785</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>3285574.5211948</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>3373543.96830096</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>3316084.58972</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>3249801.39741351</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>3578671.50054565</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>4115301.26386587</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>4904674.42694353</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>5124591.48593073</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>5394953.78242375</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>6297565.08436557</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>927.979</t>
+          <t>704861.697415182</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>814.457</t>
+          <t>717204.956011211</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>845.996</t>
+          <t>739668.828371792</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>976.538</t>
+          <t>774560.756860511</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1064.162</t>
+          <t>809994.425963053</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1208.881</t>
+          <t>863088.268945091</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1296.362</t>
+          <t>893154.834139379</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1245.406</t>
+          <t>890083.004289131</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1178.891</t>
+          <t>912867.143363989</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>978.453</t>
+          <t>938179.502041366</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>889.765</t>
+          <t>978614.593700576</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>762.661</t>
+          <t>1009930.5478757</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>572.038</t>
+          <t>1041060.7112423</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>410.156</t>
+          <t>1032442.29769058</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>428.085</t>
+          <t>1023323.8990226</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>609344.664262209</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>620383.656677345</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>643756.219903232</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>678743.230153769</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>711910.160967824</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>762181.992895343</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>789673.831616382</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>785132.006246717</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>799473.780840878</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>822591.64493767</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>858082.963645492</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>883884.88869262</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>909819.950108982</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>903492.72797568</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>889808.724787288</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>342655.188134818</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>371105.94570135</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>409174.961685109</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>430547.159193833</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>430488.346601196</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>411270.373080787</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>398643.805066398</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>455726.072201287</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>528949.505197663</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>641775.470289546</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>646449.28218429</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>701803.651607263</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>805411.712864362</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>793923.820217562</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>592527.649649153</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>49007345311986.8</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>44164060903634.8</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>49307163785366.1</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>59693240769182</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>68123345223347.2</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>76044384386223.9</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>79590257404258.4</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>84323734198176.8</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>94070226091230.1</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>88967882309291.1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>83548522485408.6</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>74625157542974.6</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>62575829021353.2</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>43196992453596.4</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>34902210340739.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>57429599716383.7</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>53829383813310.9</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>62724831004511.3</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>77051879776253.1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>86890819214967.5</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>100765769381218</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>109072598270824</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>114482257810270</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>126122683432007</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>125069336713172</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>117320454809254</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>108052735453782</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>93541825678335.5</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>66428094300199.9</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>55560473060145</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>29621016281472.1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>27368040236230.4</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>31287931399119.1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>37606327127538.9</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>41524615185387.8</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>47094623004038.4</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>49997622605110.1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>52463379315990.2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>57358898411760.4</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>56559909277539.9</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>53152791017834.7</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>48918524468112.5</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>42001349275354</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>29914246616961</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>24967604621280.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>27913387.7468886</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>28163684.9898958</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>28630138.8273842</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>28879660.1410479</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>29267235.4487518</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>29617096.5365194</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>29924752.1919734</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>30105879.5400161</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>30408163.3871446</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>30703397.31174</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>31090257.8953786</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>31398264.8920847</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>31601986.058387</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>31673802.9339179</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>30972251.5790757</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>23964000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>24245000</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>24790000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>25156000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>25577000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>26013000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>26297000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>26409000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>26475000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>26731000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>27093000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>27310000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>27438000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>27505000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>26766000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>44993802000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>45389552000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>46176543000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>46487590000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>46808741000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>47050896000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>47522650000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>47355712000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>47271276000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>47631936000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>48233604000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>48510801000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>48898444000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>48638184000</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>47697788000</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>38627753854.3556</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>39074066076.0412</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>39982918276.1454</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>40493614132.8693</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>40906739232.4566</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>41325285081.1633</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>41761519662.1478</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>41540623204.3714</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>41156942501.4695</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>41469328891.795</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>42032235228.4587</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>42194369015.7217</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>42455417327.0363</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>42236584401.0295</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>41220089871.3641</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.277767528904053</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.28488409319564</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.299234247700508</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.316493571632793</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.329116537176529</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.347523843868929</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.350137638080635</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.360656736409175</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.361891037278401</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.355932378530736</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.361792155573614</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.372400404706165</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.389528465053993</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.399501116619149</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.398407637829891</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.415303017138807</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.416234283839518</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.435409014035973</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.433675026228324</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.432040079440748</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.420134869664512</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.412186031559375</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.413691429736799</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.431608389644541</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.446891177916702</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.444916896543453</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.442551596604485</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.422380180206385</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.417104646342857</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.427590105531019</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.30692945395714</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.298881622964842</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.265356738263519</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.249831402138882</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.238843383382723</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.232341286466559</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.23767633035999</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.225651833854026</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.206500573077058</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.197176443552562</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.193290947882933</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.185047998689349</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.188091354739622</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.183394237037994</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.17400225663909</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.189766274996681</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.190379047097163</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.203799425594425</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.216388318268939</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.230560399126563</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.243414760669638</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.248715498768196</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.258058419418581</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.259437706930295</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.255510329270998</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.259812932362462</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.269235322839665</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.28630327573404</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.28719214049374</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.290226513831573</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.433241589076702</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.440991399183517</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.463079372051525</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.463273795379137</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.463675712205606</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.458116574755566</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.449818700886118</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.455396582149686</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.476733137253857</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.491909929449492</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.492288182470444</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.489822794062092</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.468380014306229</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.472070456315513</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.479810922968492</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.376992135926617</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.36862955371932</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.33312120235405</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.320337886351924</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.305763888667831</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.298468664574796</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.301465800345686</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.286544998431733</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.263829155815847</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.25257974127951</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.247898885167095</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.240941883098243</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.245316709959732</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.240737403190748</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.229962563199935</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2101260.81717</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2220947.3865</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2459925.23759</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2637347.57813</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2712196.54421</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2687524.70806</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2668744.08914</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2908661.31497</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>3332392.14615</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>3941733.15299</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>4191589.31804</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>4487219.69286</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>5139696.58206</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>4908990.5134</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>4002420.38558</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1047516.88555</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1100347.37222</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1217407.20315</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1310780.13128</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1343247.17625</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1325745.66129</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1319582.23015</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1458373.53539</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1684919.42233</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2004599.18394</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2072674.67191</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2224544.26258</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2556704.64799</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2451685.96675</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2008379.50882</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1750849.27053902</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1797714.07422874</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1850266.51528009</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1921140.27809232</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1991368.44787993</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2066078.15091517</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2140835.62887224</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2215228.67333853</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>2284620.07971019</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2361715.48426028</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2443562.40256436</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2531603.63459202</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2632783.32126529</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
